--- a/public/static/产品工序质量单价导入模板.xlsx
+++ b/public/static/产品工序质量单价导入模板.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500" activeTab="1"/>
+    <workbookView windowWidth="11424" windowHeight="5352"/>
   </bookViews>
   <sheets>
-    <sheet name="产品工序单价" sheetId="1" r:id="rId1"/>
+    <sheet name="产品工序质量单价" sheetId="1" r:id="rId1"/>
     <sheet name="说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -34,6 +34,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>品名规格(</t>
     </r>
     <r>
@@ -59,6 +66,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>工序编码(</t>
     </r>
     <r>
@@ -148,6 +162,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>生效日期(</t>
     </r>
     <r>
